--- a/data/trans_orig/IP31KM15_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM15_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54238</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>73984</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,92%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>50806</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>41809</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>59661</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>49,95%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>51653</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56411</t>
+          <t>43950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81481</t>
+          <t>59812</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>120815</t>
+          <t>115798</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106580</t>
+          <t>103495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136183</t>
+          <t>128647</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57064</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47225</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>66971</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,08%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>55,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>50903</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42048</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>59900</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>50,05%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65167</t>
+          <t>48696</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53695</t>
+          <t>40537</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78765</t>
+          <t>56399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>116071</t>
+          <t>105760</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100703</t>
+          <t>92911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130306</t>
+          <t>118063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>53,29%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53523</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>45134</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>61781</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>59,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>50,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>68,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>60246</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>52758</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>67657</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>64,51%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>56,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>72,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55029</t>
+          <t>61686</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46625</t>
+          <t>53679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63084</t>
+          <t>69657</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>115275</t>
+          <t>115209</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104429</t>
+          <t>103992</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126693</t>
+          <t>126305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>68,17%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36357</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28099</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44746</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>40,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>31,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>49,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>33146</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25735</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40634</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>35,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>43,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>38679</t>
+          <t>33724</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30624</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47083</t>
+          <t>41731</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>71826</t>
+          <t>70081</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60408</t>
+          <t>58985</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82672</t>
+          <t>81298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33466</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26617</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39135</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>59,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>33701</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27882</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39555</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>67,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36302</t>
+          <t>34197</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29013</t>
+          <t>26626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>40046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>70002</t>
+          <t>67663</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60284</t>
+          <t>56904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79207</t>
+          <t>76067</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22378</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16709</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>29227</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>52,34%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16388</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10534</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>22207</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>32,72%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>17813</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>11964</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33321</t>
+          <t>25384</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>42420</t>
+          <t>40191</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33215</t>
+          <t>31787</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52138</t>
+          <t>50950</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>104154</t>
+          <t>114875</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71720</t>
+          <t>100978</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125882</t>
+          <t>128717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>121638</t>
+          <t>97504</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105058</t>
+          <t>84567</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>135710</t>
+          <t>108422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>225792</t>
+          <t>212378</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182658</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250049</t>
+          <t>231901</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>62,01%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82438</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>68596</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>96335</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>41,78%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>34,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>48,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>111383</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>89655</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>143817</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>51,68%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>41,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>66,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>91020</t>
+          <t>79136</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76948</t>
+          <t>68218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107600</t>
+          <t>92073</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>202404</t>
+          <t>161575</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178147</t>
+          <t>142052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245538</t>
+          <t>178562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>75207</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>62263</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>91826</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>51,66%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42,77%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>63,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>67134</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>56790</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>75470</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>58,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>83164</t>
+          <t>68965</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70263</t>
+          <t>60474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99915</t>
+          <t>77771</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>150298</t>
+          <t>144172</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133191</t>
+          <t>129124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169271</t>
+          <t>161676</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>53760</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>83323</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>48,34%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>57,23%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>48375</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>40039</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>58719</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>41,88%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>50,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>76297</t>
+          <t>46501</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59546</t>
+          <t>37695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89198</t>
+          <t>54992</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>124672</t>
+          <t>116880</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105699</t>
+          <t>99376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>141779</t>
+          <t>131928</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>50,54%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>29798</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>22752</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>37616</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>45,24%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>34,54%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>57,11%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>41576</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>34764</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>48039</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>60,35%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>50,46%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>69,73%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29735</t>
+          <t>42141</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>34483</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>48792</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>71310</t>
+          <t>71940</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60809</t>
+          <t>61418</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81842</t>
+          <t>82155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>60,31%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>36065</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>28247</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>43111</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>54,76%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>42,89%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>65,46%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>27319</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>20856</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>34131</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>39,65%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>30,27%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>49,54%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>39296</t>
+          <t>28215</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31844</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>35873</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>66615</t>
+          <t>64280</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56083</t>
+          <t>54065</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77116</t>
+          <t>74802</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>371014</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>342953</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>394890</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,91%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>50,76%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>58,44%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>357616</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>308968</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>387917</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>55,43%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>47,89%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>60,13%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>395876</t>
+          <t>356147</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>367452</t>
+          <t>334907</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>424124</t>
+          <t>377364</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>753492</t>
+          <t>727161</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>704307</t>
+          <t>694942</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>795024</t>
+          <t>760048</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>59,11%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>304681</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>280805</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>332742</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>45,09%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>41,56%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>49,24%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>374</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>287515</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>257214</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>336163</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>44,57%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>52,11%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>336492</t>
+          <t>254085</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>308244</t>
+          <t>232868</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>364916</t>
+          <t>275325</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>624007</t>
+          <t>558766</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>582475</t>
+          <t>525879</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>673192</t>
+          <t>590985</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
